--- a/results/Int Task Remove ACC 0.3/Rando_4_permute.xlsx
+++ b/results/Int Task Remove ACC 0.3/Rando_4_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7722302059339223</v>
+        <v>0.7564661188847251</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7345779901674288</v>
+        <v>0.7458032798157253</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7213961563585107</v>
+        <v>0.7515494894626464</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7080737099047685</v>
+        <v>0.7515494894626464</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7138171691821089</v>
+        <v>0.7689201361432942</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7103888334995014</v>
+        <v>0.7702760683466841</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7234080517069481</v>
+        <v>0.7680713033313852</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7418482483583732</v>
+        <v>0.7689201361432942</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7235431636126104</v>
+        <v>0.7648495891635438</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7294767421872315</v>
+        <v>0.7668834874686286</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7225537181558772</v>
+        <v>0.7668834874686286</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7225537181558772</v>
+        <v>0.7596022277993606</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7030498160690343</v>
+        <v>0.7365431292329907</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6845683638738955</v>
+        <v>0.7533049128476639</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6776480902121222</v>
+        <v>0.7580809296249184</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6838986488809434</v>
+        <v>0.7584199126757658</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6828816997284011</v>
+        <v>0.7509677862962836</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6416192800907622</v>
+        <v>0.7755261800804483</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6336710557981229</v>
+        <v>0.7876993158455667</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6202798501048579</v>
+        <v>0.7868504830336576</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6196046343727438</v>
+        <v>0.7937927596520783</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6204287138584248</v>
+        <v>0.8068009763812012</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6202605975177915</v>
+        <v>0.8086502561281672</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6273489875201981</v>
+        <v>0.783047409495651</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6200512256334445</v>
+        <v>0.7838934919379792</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.63019596383264</v>
+        <v>0.7881376559975246</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6173641145528931</v>
+        <v>0.772709801629594</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6056980781792554</v>
+        <v>0.7764276137105923</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6053425929109224</v>
+        <v>0.750714408498642</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6095840066008871</v>
+        <v>0.7567996011964109</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5953742221611029</v>
+        <v>0.7540877367896311</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5728937325953175</v>
+        <v>0.7540877367896311</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5372396603293568</v>
+        <v>0.6648162409323752</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5384219754529515</v>
+        <v>0.6493691339773782</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5284618558118748</v>
+        <v>0.5718186818853783</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5086241276171486</v>
+        <v>0.5718186818853783</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4998380719909238</v>
+        <v>0.5942909203424209</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.4998380719909238</v>
+        <v>0.586240932375288</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.4907157836834325</v>
+        <v>0.5643421459758655</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.4673699590882525</v>
+        <v>0.5392158008732424</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.4927826864234882</v>
+        <v>0.5310389521091896</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5272021865438168</v>
+        <v>0.5408557087358614</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.4930831643002028</v>
+        <v>0.4680183587169526</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.484297108673978</v>
+        <v>0.462779248461512</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.4793694777735759</v>
+        <v>0.4158146250902465</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.4838147626087256</v>
+        <v>0.4176253996630797</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.4587905249767937</v>
+        <v>0.4927692783717812</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.4780991508233918</v>
+        <v>0.4927692783717812</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.4703602984150995</v>
+        <v>0.4912479801973391</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.468670883900024</v>
+        <v>0.4351810086980438</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.471052016364699</v>
+        <v>0.450479251899474</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.471052016364699</v>
+        <v>0.4472410355141472</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.4880922748994396</v>
+        <v>0.4198078179255337</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.4752136693368171</v>
+        <v>0.4203149173170144</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.4491037233128202</v>
+        <v>0.4348083336198302</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.4468879568191976</v>
+        <v>0.4405270395709424</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.3946763158799463</v>
+        <v>0.4618582184481039</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.410999415546464</v>
+        <v>0.4371341148966892</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.4104923161549833</v>
+        <v>0.4230016846013683</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.4023512221954825</v>
+        <v>0.4240134768109465</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.3848781242479458</v>
+        <v>0.4263175989273559</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.3358606937807268</v>
+        <v>0.4403950218310586</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.3417942723553478</v>
+        <v>0.4437518479045621</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.3417942723553478</v>
+        <v>0.4134087392993434</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.3414552893045003</v>
+        <v>0.4853560009626293</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.3081606903427648</v>
+        <v>0.4476656238182005</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.3052312029428955</v>
+        <v>0.4442895451576305</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.3194602399697459</v>
+        <v>0.5001884003162925</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.3199700897308076</v>
+        <v>0.4990033348231169</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.3199700897308076</v>
+        <v>0.427226939870045</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.3329614604462475</v>
+        <v>0.4747653590951284</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.3218468731735827</v>
+        <v>0.4466875236359886</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.3997827208031079</v>
+        <v>0.4518661257606491</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.3879513184584178</v>
+        <v>0.4317915219857668</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.3908147969883453</v>
+        <v>0.5410052600818235</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4107955444012789</v>
+        <v>0.5336872142194107</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4084281637845085</v>
+        <v>0.53318011482793</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4497758448791556</v>
+        <v>0.455285866538316</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5551390655619349</v>
+        <v>0.4390975349812631</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5329673049816069</v>
+        <v>0.4215171726200708</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5874335613848111</v>
+        <v>0.4443283941279609</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.6318901914944821</v>
+        <v>0.4422202358441916</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.6318901914944821</v>
+        <v>0.3989380135455702</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5266806477120363</v>
+        <v>0.4296644549111287</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5266806477120363</v>
+        <v>0.4386653831608622</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.509599133633582</v>
+        <v>0.4672338157939974</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5072097500601643</v>
+        <v>0.4960611269639358</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4929614604462475</v>
+        <v>0.5007487881184034</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4924543610547668</v>
+        <v>0.5043180802420325</v>
       </c>
     </row>
   </sheetData>
